--- a/artfynd/A 25818-2020 artfynd.xlsx
+++ b/artfynd/A 25818-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 25818-2020 artfynd.xlsx
+++ b/artfynd/A 25818-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AY40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5451,6 +5451,120 @@
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>114933036</v>
+      </c>
+      <c r="B40" t="n">
+        <v>83001</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Örstigsnäs  Ö, Srm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>621715</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6511652</v>
+      </c>
+      <c r="S40" t="n">
+        <v>25</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Annika Fritsch</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Annika Fritsch</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25818-2020 artfynd.xlsx
+++ b/artfynd/A 25818-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY40"/>
+  <dimension ref="A1:AY42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5565,6 +5565,248 @@
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>123098910</v>
+      </c>
+      <c r="B41" t="n">
+        <v>83376</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Örstigsnäs nära grustaget - lokal 2, Srm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>621703</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6511669</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>äldre barrskog på isälvsgrus på störda - delvis mosstäcka ytor. Granarna omkring är gröna och helt friska.</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>äldre, grandominerad barrskog</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>123098909</v>
+      </c>
+      <c r="B42" t="n">
+        <v>90380</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>2008</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Fyrflikig jordstjärna</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Geastrum quadrifidum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Örstigsnäs nära grustaget - lokal 2, Srm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>621703</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6511669</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>äldre barrskog på isälvsgrus på störda - delvis mosstäcka ytor. Granarna omkring är gröna och helt friska.</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>äldre, grandominerad barrskog</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25818-2020 artfynd.xlsx
+++ b/artfynd/A 25818-2020 artfynd.xlsx
@@ -5691,7 +5691,7 @@
         <v>123098909</v>
       </c>
       <c r="B42" t="n">
-        <v>90380</v>
+        <v>90388</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>

--- a/artfynd/A 25818-2020 artfynd.xlsx
+++ b/artfynd/A 25818-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AY44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5807,6 +5807,248 @@
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>123312485</v>
+      </c>
+      <c r="B43" t="n">
+        <v>83376</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Örstigsnässkogen, Örstigsnäs gård, Srm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>621715</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6511663</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>17:47</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Markus Forsberg</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Markus Forsberg</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>123312886</v>
+      </c>
+      <c r="B44" t="n">
+        <v>83376</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Granskog ca 800m O Örstigsnäsgård, 125m SV trevägskors, Srm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>621708</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6511660</v>
+      </c>
+      <c r="S44" t="n">
+        <v>25</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>18:07</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Markus Forsberg</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Markus Forsberg</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25818-2020 artfynd.xlsx
+++ b/artfynd/A 25818-2020 artfynd.xlsx
@@ -5567,10 +5567,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123098910</v>
+        <v>123098909</v>
       </c>
       <c r="B41" t="n">
-        <v>83376</v>
+        <v>90391</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5579,30 +5579,30 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1445</v>
+        <v>2008</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5688,10 +5688,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123098909</v>
+        <v>123098910</v>
       </c>
       <c r="B42" t="n">
-        <v>90388</v>
+        <v>83379</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5700,30 +5700,30 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2008</v>
+        <v>1445</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5812,7 +5812,7 @@
         <v>123312485</v>
       </c>
       <c r="B43" t="n">
-        <v>83376</v>
+        <v>83379</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         <v>123312886</v>
       </c>
       <c r="B44" t="n">
-        <v>83376</v>
+        <v>83379</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>

--- a/artfynd/A 25818-2020 artfynd.xlsx
+++ b/artfynd/A 25818-2020 artfynd.xlsx
@@ -5570,7 +5570,7 @@
         <v>123098909</v>
       </c>
       <c r="B41" t="n">
-        <v>90391</v>
+        <v>90393</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>123098910</v>
       </c>
       <c r="B42" t="n">
-        <v>83379</v>
+        <v>83381</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         <v>123312485</v>
       </c>
       <c r="B43" t="n">
-        <v>83379</v>
+        <v>83381</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         <v>123312886</v>
       </c>
       <c r="B44" t="n">
-        <v>83379</v>
+        <v>83381</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>

--- a/artfynd/A 25818-2020 artfynd.xlsx
+++ b/artfynd/A 25818-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY44"/>
+  <dimension ref="A1:AY46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6049,6 +6049,236 @@
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>123511134</v>
+      </c>
+      <c r="B45" t="n">
+        <v>83383</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Näslandet, Srm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>621663</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6511638</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På kolbottnen (?) västerut</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Agnes Eriksson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Agnes Eriksson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>123511131</v>
+      </c>
+      <c r="B46" t="n">
+        <v>83383</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Näslandet, Srm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>621679</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6511637</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>på kolbottnen (?) åt öster</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Agnes Eriksson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Agnes Eriksson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25818-2020 artfynd.xlsx
+++ b/artfynd/A 25818-2020 artfynd.xlsx
@@ -5570,7 +5570,7 @@
         <v>123098909</v>
       </c>
       <c r="B41" t="n">
-        <v>90393</v>
+        <v>90399</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>123098910</v>
       </c>
       <c r="B42" t="n">
-        <v>83381</v>
+        <v>83383</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5809,10 +5809,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123312485</v>
+        <v>123312886</v>
       </c>
       <c r="B43" t="n">
-        <v>83381</v>
+        <v>83383</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5844,25 +5844,29 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr"/>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Örstigsnässkogen, Örstigsnäs gård, Srm</t>
+          <t>Granskog ca 800m O Örstigsnäsgård, 125m SV trevägskors, Srm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>621715</v>
+        <v>621708</v>
       </c>
       <c r="R43" t="n">
-        <v>6511663</v>
+        <v>6511660</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5891,7 +5895,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5901,7 +5905,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5928,10 +5932,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123312886</v>
+        <v>123312485</v>
       </c>
       <c r="B44" t="n">
-        <v>83381</v>
+        <v>83383</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5963,29 +5967,25 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Granskog ca 800m O Örstigsnäsgård, 125m SV trevägskors, Srm</t>
+          <t>Örstigsnässkogen, Örstigsnäs gård, Srm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>621708</v>
+        <v>621715</v>
       </c>
       <c r="R44" t="n">
-        <v>6511660</v>
+        <v>6511663</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6024,7 +6024,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6051,7 +6051,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123511134</v>
+        <v>123511131</v>
       </c>
       <c r="B45" t="n">
         <v>83383</v>
@@ -6086,7 +6086,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J45" t="inlineStr"/>
@@ -6098,10 +6098,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>621663</v>
+        <v>621679</v>
       </c>
       <c r="R45" t="n">
-        <v>6511638</v>
+        <v>6511637</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På kolbottnen (?) västerut</t>
+          <t>på kolbottnen (?) åt öster</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6166,7 +6166,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123511131</v>
+        <v>123511134</v>
       </c>
       <c r="B46" t="n">
         <v>83383</v>
@@ -6201,7 +6201,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J46" t="inlineStr"/>
@@ -6213,10 +6213,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>621679</v>
+        <v>621663</v>
       </c>
       <c r="R46" t="n">
-        <v>6511637</v>
+        <v>6511638</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>på kolbottnen (?) åt öster</t>
+          <t>På kolbottnen (?) västerut</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 25818-2020 artfynd.xlsx
+++ b/artfynd/A 25818-2020 artfynd.xlsx
@@ -5567,10 +5567,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123098909</v>
+        <v>123098910</v>
       </c>
       <c r="B41" t="n">
-        <v>90399</v>
+        <v>83386</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5579,30 +5579,30 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2008</v>
+        <v>1445</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5688,10 +5688,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123098910</v>
+        <v>123098909</v>
       </c>
       <c r="B42" t="n">
-        <v>83383</v>
+        <v>90402</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5700,30 +5700,30 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1445</v>
+        <v>2008</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5812,7 +5812,7 @@
         <v>123312886</v>
       </c>
       <c r="B43" t="n">
-        <v>83383</v>
+        <v>83386</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5935,7 +5935,7 @@
         <v>123312485</v>
       </c>
       <c r="B44" t="n">
-        <v>83383</v>
+        <v>83386</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6051,10 +6051,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123511131</v>
+        <v>123511134</v>
       </c>
       <c r="B45" t="n">
-        <v>83383</v>
+        <v>83386</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6086,7 +6086,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J45" t="inlineStr"/>
@@ -6098,10 +6098,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>621679</v>
+        <v>621663</v>
       </c>
       <c r="R45" t="n">
-        <v>6511637</v>
+        <v>6511638</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>på kolbottnen (?) åt öster</t>
+          <t>På kolbottnen (?) västerut</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6166,10 +6166,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123511134</v>
+        <v>123511131</v>
       </c>
       <c r="B46" t="n">
-        <v>83383</v>
+        <v>83386</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6201,7 +6201,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J46" t="inlineStr"/>
@@ -6213,10 +6213,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>621663</v>
+        <v>621679</v>
       </c>
       <c r="R46" t="n">
-        <v>6511638</v>
+        <v>6511637</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På kolbottnen (?) västerut</t>
+          <t>på kolbottnen (?) åt öster</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 25818-2020 artfynd.xlsx
+++ b/artfynd/A 25818-2020 artfynd.xlsx
@@ -5567,10 +5567,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123098910</v>
+        <v>123098909</v>
       </c>
       <c r="B41" t="n">
-        <v>83386</v>
+        <v>90419</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5579,30 +5579,30 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1445</v>
+        <v>2008</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5688,10 +5688,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123098909</v>
+        <v>123098910</v>
       </c>
       <c r="B42" t="n">
-        <v>90402</v>
+        <v>83395</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5700,30 +5700,30 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2008</v>
+        <v>1445</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5812,7 +5812,7 @@
         <v>123312886</v>
       </c>
       <c r="B43" t="n">
-        <v>83386</v>
+        <v>83395</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5935,7 +5935,7 @@
         <v>123312485</v>
       </c>
       <c r="B44" t="n">
-        <v>83386</v>
+        <v>83395</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         <v>123511134</v>
       </c>
       <c r="B45" t="n">
-        <v>83386</v>
+        <v>83395</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         <v>123511131</v>
       </c>
       <c r="B46" t="n">
-        <v>83386</v>
+        <v>83395</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>

--- a/artfynd/A 25818-2020 artfynd.xlsx
+++ b/artfynd/A 25818-2020 artfynd.xlsx
@@ -5570,7 +5570,7 @@
         <v>123098909</v>
       </c>
       <c r="B41" t="n">
-        <v>90419</v>
+        <v>90424</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>123098910</v>
       </c>
       <c r="B42" t="n">
-        <v>83395</v>
+        <v>83400</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         <v>123312886</v>
       </c>
       <c r="B43" t="n">
-        <v>83395</v>
+        <v>83400</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5935,7 +5935,7 @@
         <v>123312485</v>
       </c>
       <c r="B44" t="n">
-        <v>83395</v>
+        <v>83400</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         <v>123511134</v>
       </c>
       <c r="B45" t="n">
-        <v>83395</v>
+        <v>83400</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         <v>123511131</v>
       </c>
       <c r="B46" t="n">
-        <v>83395</v>
+        <v>83400</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>

--- a/artfynd/A 25818-2020 artfynd.xlsx
+++ b/artfynd/A 25818-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AY43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5453,14 +5453,14 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>114933036</v>
+        <v>123098910</v>
       </c>
       <c r="B40" t="n">
-        <v>83054</v>
+        <v>83402</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5496,21 +5496,19 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Örstigsnäs  Ö, Srm</t>
+          <t>Örstigsnäs nära grustaget - lokal 2, Srm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>621715</v>
+        <v>621703</v>
       </c>
       <c r="R40" t="n">
-        <v>6511652</v>
+        <v>6511669</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5534,12 +5532,17 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>äldre barrskog på isälvsgrus på störda - delvis mosstäcka ytor. Granarna omkring är gröna och helt friska.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5548,19 +5551,23 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>äldre, grandominerad barrskog</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Annika Fritsch</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Annika Fritsch</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5570,7 +5577,7 @@
         <v>123098909</v>
       </c>
       <c r="B41" t="n">
-        <v>90424</v>
+        <v>90426</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5688,10 +5695,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123098910</v>
+        <v>123511134</v>
       </c>
       <c r="B42" t="n">
-        <v>83400</v>
+        <v>83402</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5723,24 +5730,22 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Örstigsnäs nära grustaget - lokal 2, Srm</t>
+          <t>Näslandet, Srm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>621703</v>
+        <v>621663</v>
       </c>
       <c r="R42" t="n">
-        <v>6511669</v>
+        <v>6511638</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5767,17 +5772,17 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>äldre barrskog på isälvsgrus på störda - delvis mosstäcka ytor. Granarna omkring är gröna och helt friska.</t>
+          <t>På kolbottnen (?) västerut</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5786,33 +5791,29 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>äldre, grandominerad barrskog</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Agnes Eriksson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Agnes Eriksson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123312886</v>
+        <v>123511131</v>
       </c>
       <c r="B43" t="n">
-        <v>83400</v>
+        <v>83402</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5844,29 +5845,25 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Granskog ca 800m O Örstigsnäsgård, 125m SV trevägskors, Srm</t>
+          <t>Näslandet, Srm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>621708</v>
+        <v>621679</v>
       </c>
       <c r="R43" t="n">
-        <v>6511660</v>
+        <v>6511637</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5890,22 +5887,17 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>17:57</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>18:07</t>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>på kolbottnen (?) åt öster</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5914,370 +5906,22 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Markus Forsberg</t>
+          <t>Agnes Eriksson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Markus Forsberg</t>
+          <t>Agnes Eriksson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>123312485</v>
-      </c>
-      <c r="B44" t="n">
-        <v>83400</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>1445</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Bombmurkla</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Sarcosoma globosum</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>Örstigsnässkogen, Örstigsnäs gård, Srm</t>
-        </is>
-      </c>
-      <c r="Q44" t="n">
-        <v>621715</v>
-      </c>
-      <c r="R44" t="n">
-        <v>6511663</v>
-      </c>
-      <c r="S44" t="n">
-        <v>10</v>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>Nyköping</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>Nyköping</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>17:47</t>
-        </is>
-      </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>17:53</t>
-        </is>
-      </c>
-      <c r="AD44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT44" t="inlineStr"/>
-      <c r="AW44" t="inlineStr">
-        <is>
-          <t>Markus Forsberg</t>
-        </is>
-      </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>Markus Forsberg</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>123511134</v>
-      </c>
-      <c r="B45" t="n">
-        <v>83400</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>1445</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Bombmurkla</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Sarcosoma globosum</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>Näslandet, Srm</t>
-        </is>
-      </c>
-      <c r="Q45" t="n">
-        <v>621663</v>
-      </c>
-      <c r="R45" t="n">
-        <v>6511638</v>
-      </c>
-      <c r="S45" t="n">
-        <v>10</v>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>Nyköping</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>Nyköping</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>2025-03-16</t>
-        </is>
-      </c>
-      <c r="AA45" t="inlineStr">
-        <is>
-          <t>2025-03-16</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På kolbottnen (?) västerut</t>
-        </is>
-      </c>
-      <c r="AD45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF45" t="inlineStr"/>
-      <c r="AG45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT45" t="inlineStr"/>
-      <c r="AW45" t="inlineStr">
-        <is>
-          <t>Agnes Eriksson</t>
-        </is>
-      </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>Agnes Eriksson</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>123511131</v>
-      </c>
-      <c r="B46" t="n">
-        <v>83400</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>1445</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Bombmurkla</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Sarcosoma globosum</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>Näslandet, Srm</t>
-        </is>
-      </c>
-      <c r="Q46" t="n">
-        <v>621679</v>
-      </c>
-      <c r="R46" t="n">
-        <v>6511637</v>
-      </c>
-      <c r="S46" t="n">
-        <v>10</v>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>Nyköping</t>
-        </is>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W46" t="inlineStr">
-        <is>
-          <t>Nyköping</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>2025-03-16</t>
-        </is>
-      </c>
-      <c r="AA46" t="inlineStr">
-        <is>
-          <t>2025-03-16</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>på kolbottnen (?) åt öster</t>
-        </is>
-      </c>
-      <c r="AD46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF46" t="inlineStr"/>
-      <c r="AG46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT46" t="inlineStr"/>
-      <c r="AW46" t="inlineStr">
-        <is>
-          <t>Agnes Eriksson</t>
-        </is>
-      </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>Agnes Eriksson</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25818-2020 artfynd.xlsx
+++ b/artfynd/A 25818-2020 artfynd.xlsx
@@ -5695,7 +5695,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123511134</v>
+        <v>123511131</v>
       </c>
       <c r="B42" t="n">
         <v>83402</v>
@@ -5730,7 +5730,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J42" t="inlineStr"/>
@@ -5742,10 +5742,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>621663</v>
+        <v>621679</v>
       </c>
       <c r="R42" t="n">
-        <v>6511638</v>
+        <v>6511637</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På kolbottnen (?) västerut</t>
+          <t>på kolbottnen (?) åt öster</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5810,7 +5810,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123511131</v>
+        <v>123511134</v>
       </c>
       <c r="B43" t="n">
         <v>83402</v>
@@ -5845,7 +5845,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J43" t="inlineStr"/>
@@ -5857,10 +5857,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>621679</v>
+        <v>621663</v>
       </c>
       <c r="R43" t="n">
-        <v>6511637</v>
+        <v>6511638</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>på kolbottnen (?) åt öster</t>
+          <t>På kolbottnen (?) västerut</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 25818-2020 artfynd.xlsx
+++ b/artfynd/A 25818-2020 artfynd.xlsx
@@ -5695,7 +5695,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123511131</v>
+        <v>123511134</v>
       </c>
       <c r="B42" t="n">
         <v>83402</v>
@@ -5730,7 +5730,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J42" t="inlineStr"/>
@@ -5742,10 +5742,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>621679</v>
+        <v>621663</v>
       </c>
       <c r="R42" t="n">
-        <v>6511637</v>
+        <v>6511638</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>på kolbottnen (?) åt öster</t>
+          <t>På kolbottnen (?) västerut</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5810,7 +5810,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123511134</v>
+        <v>123511131</v>
       </c>
       <c r="B43" t="n">
         <v>83402</v>
@@ -5845,7 +5845,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J43" t="inlineStr"/>
@@ -5857,10 +5857,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>621663</v>
+        <v>621679</v>
       </c>
       <c r="R43" t="n">
-        <v>6511638</v>
+        <v>6511637</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På kolbottnen (?) västerut</t>
+          <t>på kolbottnen (?) åt öster</t>
         </is>
       </c>
       <c r="AD43" t="b">
